--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0192.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0192.xlsx
@@ -1939,7 +1939,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Ngươi! Nhắc lại cho ta nghe! Xem ngươi có thực sự nghe không đấy.</t>
+          <t>Mày! Nhắc lại cho tao nghe! Xem mày có thực sự nghe không đấy.</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>SAI BÉT! Còn lâu mới đúng! Cậu có nghe được một chữ nào không vậy?!</t>
+          <t>SAI BÉT! Còn lâu mới đúng! Mày có nghe được một chữ nào không vậy?!</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Ta một mình đánh cả bầy Kerasaurs, di chuyển nhanh như đại bàng...</t>
+          <t>Tao một mình đánh cả bầy Kerasaurs, di chuyển nhanh như đại bàng...</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Ê! Ta đâu có làm cái đó! Cần nói thêm bao nhiêu lần nữa hả?!</t>
+          <t>Ê! Tao đâu có làm cái đó! Cần nói thêm bao nhiêu lần nữa hả?!</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Ha, nghe cậu mà xem. Từ bao giờ cậu lại đóng vai Nữ Tư Tế thế?</t>
+          <t>Ha, nghe mày mà xem. Từ bao giờ mày lại đóng vai Nữ Tư Tế thế?</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Ta đồng ý với cậu, Sforza. Ta cũng kính trọng Avidius.</t>
+          <t>Tao đồng ý với cậu, Sforza. Tao cũng kính trọng Avidius.</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Ôi! A-cậu là Nhà Vô Địch năm nay sao?! Tớ không ngờ lại gặp cậu ở đây! C-có thể cho tớ xin chữ ký được không ạ?</t>
+          <t>Ôi! A-bạn là Nhà Vô Địch năm nay sao?! Tớ không ngờ lại gặp bạn ở đây! C-có thể cho tớ xin chữ ký được không ạ?</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Ai mà biết? Biết đâu ta lại trở thành thợ săn giỏi hơn cả hồi còn ở đấu trường!</t>
+          <t>Ai mà biết? Biết đâu tao lại trở thành thợ săn giỏi hơn cả hồi còn ở đấu trường!</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Hừ... Ta sẽ làm cho con bé đó phải té khỏi vị trí cao ngất ấy!</t>
+          <t>Hừ... Tao sẽ làm cho con bé đó phải té khỏi vị trí cao ngất ấy!</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>À… vậy thì để ta cho ngươi một lời khuyên thân thiện. Tránh xa một Nữ Tư Tế tên là Iuno ra.</t>
+          <t>À… vậy thì để tao cho mày một lời khuyên thân thiện. Tránh xa một Nữ Tư Tế tên là Iuno ra.</t>
         </is>
       </c>
     </row>
@@ -7919,7 +7919,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Ta có thể nghe thấy tiếng hát của bọn thợ săn từ trại...</t>
+          <t>Tao có thể nghe thấy tiếng hát của bọn thợ săn từ trại...</t>
         </is>
       </c>
     </row>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Ui... trại nào? Ta chẳng thấy gì cả...</t>
+          <t>Ui... trại nào? Tao chẳng thấy gì cả...</t>
         </is>
       </c>
     </row>
@@ -13899,7 +13899,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Okay.</t>
+          <t>Ừ.</t>
         </is>
       </c>
     </row>
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Không tệ.</t>
+          <t>Khá đấy.</t>
         </is>
       </c>
     </row>
@@ -14939,7 +14939,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Amazing.</t>
+          <t>Tuyệt.</t>
         </is>
       </c>
     </row>
@@ -15199,7 +15199,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Amazing.</t>
+          <t>Tuyệt.</t>
         </is>
       </c>
     </row>
@@ -28264,7 +28264,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Không tệ.</t>
+          <t>Khá đấy.</t>
         </is>
       </c>
     </row>
@@ -28394,7 +28394,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>(Ngáp) Ta đợi ngươi đó.</t>
+          <t>(Ngáp) Tao đợi mày đó.</t>
         </is>
       </c>
     </row>
@@ -30474,7 +30474,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Ragunna là một thành phố nhộn nhịp, và những gia tộc lớn luôn có mắt khắp nơi. Không phải môi trường thân thiện cho một số "công việc" đâu. Cậu hiểu ý ta chứ?</t>
+          <t>Ragunna là một thành phố nhộn nhịp, và những gia tộc lớn luôn có mắt khắp nơi. Không phải môi trường thân thiện cho một số "công việc" đâu. Cậu hiểu ý tao chứ?</t>
         </is>
       </c>
     </row>
